--- a/analises-cross-projeto/benchmarks-estratificados/benchmarks-estratificados.xlsx
+++ b/analises-cross-projeto/benchmarks-estratificados/benchmarks-estratificados.xlsx
@@ -17,10 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'REGIAO'!$A$3:$J$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'REGIAO_PADRAO'!$A$3:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REGIAO_PADRAO_TIPOL'!$A$4:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'REGIAO_PADRAO'!$A$3:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REGIAO_PADRAO_TIPOL'!$A$4:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CLIENTE'!$A$3:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MATRIZ_MG'!$A$3:$Y$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MATRIZ_MG'!$A$3:$Y$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado 18/04/2026 13:37 . 131 projetos . 48 combinacoes</t>
+          <t>Gerado 19/04/2026 09:15 . 131 projetos . 48 combinacoes</t>
         </is>
       </c>
     </row>
@@ -702,72 +702,72 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>2271.01</v>
+        <v>1983.37</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>3217.76</v>
+        <v>3100.1619</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3755.78</v>
+        <v>3462.55</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>3799.28</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>4888.48</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>7668.2</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>9133.245000000001</v>
+        <v>7665.16</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>38409996.88</v>
+        <v>25675656.81</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>nova(4), all(2), blue(2)</t>
+          <t>pass(5), mussi(4), amalfi(3)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1519.6044</v>
+        <v>2271.01</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2758.48</v>
+        <v>2940.01</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3295.64</v>
+        <v>3755.78</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3784.64</v>
+        <v>5246.69</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>4346.61</v>
+        <v>7668.2</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>8685.715</v>
+        <v>9522.33</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>30121441.01</v>
+        <v>38409996.88</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>pass(6), chiquetti(5), mussi(4)</t>
+          <t>nova(4), blue(2), neuhaus(2)</t>
         </is>
       </c>
     </row>
@@ -778,32 +778,32 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3228.74</v>
+        <v>3378.4464</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3228.74</v>
+        <v>3378.4464</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3430.4237</v>
+        <v>3993.4387</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4358.23</v>
+        <v>4864.6625</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4358.23</v>
+        <v>4864.6625</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>7878.58</v>
+        <v>10125</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>34284020.3225</v>
+        <v>40420184.5235</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>ck(5), cn(3), adore(2)</t>
+          <t>ck(4), adore(2), cambert(2)</t>
         </is>
       </c>
     </row>
@@ -823,70 +823,70 @@
         <v>2662.81</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3036.025</v>
+        <v>3401.76</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3401.76</v>
+        <v>4196.73</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>4196.73</v>
+        <v>7159.6961</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4921.335</v>
+        <v>6681.54</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>20311698.74</v>
+        <v>23266450.125</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>amalfi(4), grandezza(2), paludo(2)</t>
+          <t>grandezza(2), all(1), amalfi(1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SP-Capital</t>
+          <t>null-Outros</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2974.22</v>
+        <v>1519.6044</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2974.22</v>
+        <v>2781.34</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3028.41</v>
+        <v>2974.48</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3082.6</v>
+        <v>3515.51</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>3082.6</v>
+        <v>4346.61</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>6001.7</v>
+        <v>10609.48</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>15642592.72</v>
+        <v>30584964.89</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>indepy(2), macom(2), ajr(1)</t>
+          <t>be(1), by(1), chiquetti(1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>RS-Serra</t>
+          <t>SC-Outros</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>2624.8</v>
@@ -895,45 +895,59 @@
         <v>2624.8</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3392.345</v>
+        <v>3650.32</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>5219.45</v>
+        <v>3732.19</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>5219.45</v>
+        <v>3732.19</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>5506.245</v>
+        <v>7040.19</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>15464874.44</v>
+        <v>18479084.15</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>paludo(3), colline(1)</t>
+          <t>mtf(2), paludo(2), chiquetti(1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros</t>
+          <t>SP-Capital</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>3028.41</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>6001.7</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>15642592.72</v>
+      </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>ck(2), santa(1)</t>
+          <t>indepy(2), macom(2), ajr(1)</t>
         </is>
       </c>
     </row>
@@ -944,7 +958,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>1604.0213</v>
@@ -969,7 +983,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>santa(2), pavcor(1)</t>
+          <t>santa(3), pavcor(1)</t>
         </is>
       </c>
     </row>
@@ -989,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1066,83 +1080,83 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>18</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>2549.1</v>
+        <v>2455.59</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3296.1</v>
+        <v>3100.1619</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>3499.745</v>
+        <v>4187.6733</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>3799.28</v>
+        <v>4344.71</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>7668.2</v>
+        <v>4888.48</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>7877.865</v>
+        <v>7966.8</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>all(2), f(2), inbrasul(2)</t>
+          <t>ck(3), amalfi(2), chiquetti(2)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2455.59</v>
+        <v>3378.4464</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3100.1619</v>
+        <v>3378.4464</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3784.64</v>
+        <v>3628.6474</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>4187.6733</v>
+        <v>4358.23</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>4344.71</v>
+        <v>4358.23</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>7815.745</v>
+        <v>9490.65</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>chiquetti(4), grupo(2), mussi(2)</t>
+          <t>ck(3), cn(2), adore(1)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1151,36 +1165,36 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3228.74</v>
+        <v>2758.48</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3228.74</v>
+        <v>3232.2</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3430.4237</v>
+        <v>3462.55</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4358.23</v>
+        <v>3722.92</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>4358.23</v>
+        <v>3799.28</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>7443.22</v>
+        <v>7013.06</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>ck(3), cn(2), muller(2)</t>
+          <t>pass(3), inbrasul(2), mussi(2)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1191,17 +1205,27 @@
       <c r="C7" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="D7" s="7" t="n">
+        <v>3217.76</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>3843.01</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>4642.46</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>6091.07</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>6123.12</v>
+      </c>
       <c r="I7" s="8" t="n">
-        <v>13188.75</v>
+        <v>7964.39</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>cambert(2), ck(2), eze(2)</t>
+          <t>nova(3), blue(2), chiquetti(1)</t>
         </is>
       </c>
     </row>
@@ -1213,71 +1237,71 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3217.76</v>
+        <v>2549.1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4345.32</v>
+        <v>2940.01</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4864.6625</v>
+        <v>3390.04</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>5246.69</v>
+        <v>3755.78</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>6123.12</v>
+        <v>7668.2</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>9133.245000000001</v>
+        <v>13025.795</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>nova(3), blue(2), caledonia(1)</t>
+          <t>viva4(2), all(1), arv(1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2758.48</v>
+        <v>4864.6625</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2974.48</v>
+        <v>4864.6625</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3443.27</v>
+        <v>4864.6625</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3732.19</v>
+        <v>4864.6625</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4346.61</v>
+        <v>4864.6625</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>10685.895</v>
+        <v>19500.94</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>pass(3), mussi(2), viva4(2)</t>
+          <t>cambert(2), adore(1), beco(1)</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1317,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>3290.71</v>
@@ -1302,7 +1326,7 @@
         <v>3290.71</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3401.76</v>
+        <v>3593.2</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>4196.73</v>
@@ -1311,18 +1335,18 @@
         <v>4196.73</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>5431.41</v>
+        <v>6681.54</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>amalfi(2), etr(1), grandezza(1)</t>
+          <t>brasin(1), etr(1), eze(1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte</t>
+          <t>null-Outros</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1334,133 +1358,171 @@
         <v>6</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1917.5902</v>
+        <v>2781.34</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1917.5902</v>
+        <v>2781.34</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>2662.81</v>
+        <v>3244.995</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2781.34</v>
+        <v>4346.61</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2781.34</v>
+        <v>4346.61</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>3476.84</v>
+        <v>8609.299999999999</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>amalfi(2), paludo(2), grandezza(1)</t>
+          <t>be(1), by(1), gdi(1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros</t>
+          <t>SC-Litoral-Norte</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="8" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1917.5902</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1917.5902</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2662.81</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>7159.6961</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>7159.6961</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>6140.53</v>
+      </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>ck(2), santa(1)</t>
+          <t>all(1), amalfi(1), grandezza(1)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-Outros</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>2271.01</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>2271.01</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>2534.04</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>2797.07</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>2797.07</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>12953.8</v>
-      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="8" t="n"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>fg(1), libra(1), neuhaus(1)</t>
+          <t>chiquetti(1), ck(1), mtf(1)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SP-Capital</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="n">
+        <v>2271.01</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>2271.01</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>2534.04</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>2797.07</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>2797.07</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>12953.8</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>fg(1), libra(1), neuhaus(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SP-Capital</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7" t="n">
         <v>2974.22</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E15" s="7" t="n">
         <v>2974.22</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <v>3028.41</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>3082.6</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>3082.6</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I15" s="8" t="n">
         <v>5179.985</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>macom(2), indepy(1)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J14"/>
+  <autoFilter ref="A3:J15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -1475,7 +1537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1585,7 +1647,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2455.59</v>
@@ -1594,23 +1656,23 @@
         <v>2455.59</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3442.4009</v>
+        <v>3643.9176</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>4187.6733</v>
+        <v>4888.48</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>4187.6733</v>
+        <v>4888.48</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>7959.45</v>
+        <v>7974.15</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>38.5</v>
+        <v>30</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>chiquetti(4), grupo(2), mussi(2)</t>
+          <t>ck(3), amalfi(2), chiquetti(2)</t>
         </is>
       </c>
     </row>
@@ -1622,123 +1684,133 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_medio_alto</t>
+          <t>residencial_vertical_alto</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2940.01</v>
+        <v>3217.76</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3483.98</v>
+        <v>3843.01</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>3619.215</v>
+        <v>4642.46</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>3799.28</v>
+        <v>6091.07</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>7668.2</v>
+        <v>6123.12</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>6443.46</v>
+        <v>7964.39</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>inbrasul(2), all(1), arv(1)</t>
+          <t>nova(3), blue(2), chiquetti(1)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_alto</t>
+          <t>residencial_vertical_medio_alto</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>2940.01</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>2940.01</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>3619.88</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>7668.2</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>7668.2</v>
+      </c>
       <c r="J7" s="8" t="n">
-        <v>13188.75</v>
+        <v>9116.129999999999</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>cambert(2), ck(2), eze(2)</t>
+          <t>viva4(2), all(1), arv(1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_alto</t>
+          <t>residencial_vertical_medio_alto</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3217.76</v>
+        <v>2758.48</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4345.32</v>
+        <v>3232.2</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>4864.6625</v>
+        <v>3595.675</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>5246.69</v>
+        <v>3722.92</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>6123.12</v>
+        <v>3799.28</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>9133.245000000001</v>
+        <v>7007.86</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>nova(3), blue(2), caledonia(1)</t>
+          <t>inbrasul(2), pass(2), brasin(1)</t>
         </is>
       </c>
     </row>
@@ -1759,16 +1831,16 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3228.74</v>
+        <v>3628.6474</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3228.74</v>
+        <v>3628.6474</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3628.6474</v>
+        <v>3993.4387</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>4358.23</v>
@@ -1777,60 +1849,60 @@
         <v>4358.23</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>4307.665</v>
+        <v>4174.83</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>20</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ck(3), muller(2), adore(1)</t>
+          <t>ck(3), adore(1), as(1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_medio_alto</t>
+          <t>residencial_vertical_alto</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2758.48</v>
+        <v>4864.6625</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2758.48</v>
+        <v>4864.6625</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>3709.52</v>
+        <v>4864.6625</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>3732.19</v>
+        <v>4864.6625</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>3732.19</v>
+        <v>4864.6625</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>10998.55</v>
+        <v>19500.94</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>127.5</v>
+        <v>46</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>pass(2), viva4(2), brasin(1)</t>
+          <t>cambert(2), adore(1), beco(1)</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1923,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>3290.71</v>
@@ -1860,7 +1932,7 @@
         <v>3290.71</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3401.76</v>
+        <v>3593.2</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>4196.73</v>
@@ -1869,21 +1941,21 @@
         <v>4196.73</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>5431.41</v>
+        <v>6681.54</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>amalfi(2), etr(1), grandezza(1)</t>
+          <t>brasin(1), etr(1), eze(1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>null-Outros</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1900,36 +1972,36 @@
         <v>4</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3232.2</v>
+        <v>2781.34</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3232.2</v>
+        <v>2781.34</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3232.2</v>
+        <v>3148.425</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>3232.2</v>
+        <v>3515.51</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>3232.2</v>
+        <v>3515.51</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>7878.58</v>
+        <v>7524.255</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>41</v>
+        <v>85.5</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>cln(1), cn(1), rosner(1)</t>
+          <t>be(1), by(1), holze(1)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1939,43 +2011,43 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_alto</t>
+          <t>residencial_vertical_medio_alto</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2974.48</v>
+        <v>3378.4464</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2974.48</v>
+        <v>3378.4464</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3295.64</v>
+        <v>3378.4464</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4346.61</v>
+        <v>3378.4464</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>4346.61</v>
+        <v>3378.4464</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>10518.78</v>
+        <v>12972.67</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>gdi(1), mabrem(1), mussi(1)</t>
+          <t>cln(1), cn(1), fonseca(1)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-Litoral-Norte</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1992,13 +2064,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2549.1</v>
+        <v>2662.81</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>2549.1</v>
+        <v>2662.81</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2634.07</v>
+        <v>4911.253</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>7159.6961</v>
@@ -2007,19 +2079,21 @@
         <v>7159.6961</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>27247.73</v>
-      </c>
-      <c r="K14" s="8" t="n"/>
+        <v>4229.335</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>f(2), all(1)</t>
+          <t>all(1), paludo(1), thozen(1)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2036,156 +2110,110 @@
         <v>3</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2662.81</v>
+        <v>3148.01</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2662.81</v>
+        <v>3148.01</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>2662.81</v>
+        <v>3295.64</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>2662.81</v>
+        <v>3443.27</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>2662.81</v>
+        <v>3443.27</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>1402.94</v>
+        <v>11552.765</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>amalfi(1), paludo(1), thozen(1)</t>
+          <t>amalfi(1), mussi(1), pass(1)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte</t>
+          <t>SC-Outros</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_medio_alto</t>
+          <t>residencial_vertical_alto</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>1917.5902</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>1917.5902</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>2349.4651</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>2781.34</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>2781.34</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>5225.33</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>90</v>
-      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>amalfi(1), grandezza(1), paludo(1)</t>
+          <t>chiquetti(1), ck(1), mtf(1)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros</t>
+          <t>SP-Capital</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_alto</t>
+          <t>residencial_vertical_medio_alto</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="E17" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>3028.41</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>5179.985</v>
+      </c>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ck(2), santa(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SP-Capital</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>residencial_vertical_medio_alto</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>2974.22</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>2974.22</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>3028.41</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>3082.6</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>3082.6</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>5179.985</v>
-      </c>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
           <t>macom(2), indepy(1)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L18"/>
+  <autoFilter ref="A4:L17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -2627,7 +2655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2794,445 +2822,453 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa | medio-alto</t>
+          <t>SC-Vale-Itajai | alto</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
         <v>18</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.79</v>
+        <v>2.23</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6.02</v>
+        <v>6.4</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>3.28</v>
+        <v>6.06</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>7.97</v>
+        <v>10.47</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>3.34</v>
+        <v>3.69</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>17.36</v>
+        <v>12.78</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>7.79</v>
+        <v>9.81</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>4.44</v>
+        <v>6.35</v>
       </c>
       <c r="N4" s="10" t="n">
-        <v>10.26</v>
+        <v>6.84</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>0.52</v>
+        <v>0.24</v>
       </c>
       <c r="Q4" s="10" t="n">
-        <v>5.07</v>
+        <v>5.42</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>4.12</v>
+        <v>4.3</v>
       </c>
       <c r="S4" s="10" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="T4" s="10" t="n">
-        <v>6.21</v>
+        <v>6.75</v>
       </c>
       <c r="U4" s="10" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="V4" s="10" t="n">
-        <v>4.21</v>
+        <v>4.65</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="X4" s="10" t="n">
-        <v>3.69</v>
+        <v>5.14</v>
       </c>
       <c r="Y4" s="10" t="n">
-        <v>18.05</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai | alto</t>
+          <t>SC-BC | medio-alto</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="D5" s="10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="S5" s="10" t="n">
         <v>2.23</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P5" s="10" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="Q5" s="10" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="R5" s="10" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="S5" s="10" t="n">
-        <v>3.61</v>
-      </c>
       <c r="T5" s="10" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="U5" s="10" t="n">
-        <v>1.04</v>
-      </c>
+        <v>11.77</v>
+      </c>
+      <c r="U5" s="10" t="n"/>
       <c r="V5" s="10" t="n">
-        <v>4.48</v>
+        <v>1.66</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>6.36</v>
+        <v>5.29</v>
       </c>
       <c r="Y5" s="10" t="n">
-        <v>20.83</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SC-BC | medio-alto</t>
+          <t>SC-Vale-Itajai | medio-alto</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>4.88</v>
+        <v>1.32</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0.48</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>7.38</v>
+        <v>7.57</v>
       </c>
       <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="n">
-        <v>8.5</v>
+        <v>7.95</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>4.21</v>
+        <v>3.54</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>12.59</v>
+        <v>13.06</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>11.47</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>6.12</v>
+        <v>5.36</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>13.23</v>
+        <v>10</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>1.31</v>
+        <v>0.74</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Q6" s="10" t="n"/>
+        <v>0.42</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>3.73</v>
+      </c>
       <c r="R6" s="10" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="S6" s="10" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T6" s="10" t="n">
-        <v>12.85</v>
+        <v>8.81</v>
       </c>
       <c r="U6" s="10" t="n"/>
       <c r="V6" s="10" t="n">
-        <v>7.98</v>
+        <v>4.51</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>5.62</v>
+        <v>5.29</v>
       </c>
       <c r="Y6" s="10" t="n">
-        <v>18.1</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-BC | alto</t>
+          <t>SC-Floripa | alto</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K7" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>11.15</v>
-      </c>
       <c r="L7" s="10" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="10" t="n"/>
+        <v>5.32</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.48</v>
+      </c>
       <c r="P7" s="10" t="n">
-        <v>0.73</v>
+        <v>1.1</v>
       </c>
       <c r="Q7" s="10" t="n"/>
       <c r="R7" s="10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S7" s="10" t="n"/>
+        <v>2.21</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>4.21</v>
+      </c>
       <c r="T7" s="10" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="U7" s="10" t="n"/>
+        <v>4.07</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>0.23</v>
+      </c>
       <c r="V7" s="10" t="n">
-        <v>5.8</v>
+        <v>6.39</v>
       </c>
       <c r="W7" s="10" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="Y7" s="10" t="n">
-        <v>23.62</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa | alto</t>
+          <t>SC-Floripa | medio-alto</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>3.77</v>
+        <v>4.45</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>6.48</v>
+        <v>6.06</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8.56</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>3.89</v>
+        <v>3.51</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>15.78</v>
+        <v>10.9</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>3.35</v>
+        <v>7.79</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>8.220000000000001</v>
+        <v>10.72</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>0.5</v>
+        <v>1.21</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q8" s="10" t="n"/>
+        <v>1.16</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>5.07</v>
+      </c>
       <c r="R8" s="10" t="n">
-        <v>2.38</v>
+        <v>4.68</v>
       </c>
       <c r="S8" s="10" t="n">
-        <v>3.86</v>
+        <v>2.45</v>
       </c>
       <c r="T8" s="10" t="n">
-        <v>5.79</v>
+        <v>7.96</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>0.23</v>
+        <v>0.88</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>5.37</v>
+        <v>5.76</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>1.29</v>
+        <v>1.92</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>4.22</v>
+        <v>3.98</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>14.64</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai | medio-alto</t>
+          <t>SC-BC | alto</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>4.49</v>
+        <v>3.77</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.45</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n">
-        <v>5.49</v>
+        <v>3.1</v>
       </c>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n">
-        <v>8.050000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>3.57</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>11.22</v>
+        <v>15.21</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>9.859999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>1.53</v>
+        <v>5.63</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>5.36</v>
+        <v>6.42</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>8.44</v>
+        <v>0.68</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.74</v>
+        <v>4.29</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="Q9" s="10" t="n"/>
       <c r="R9" s="10" t="n">
-        <v>3.72</v>
+        <v>2.56</v>
       </c>
       <c r="S9" s="10" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>8.81</v>
+        <v>9.31</v>
       </c>
       <c r="U9" s="10" t="n"/>
       <c r="V9" s="10" t="n">
-        <v>5.42</v>
+        <v>3.84</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X9" s="10" t="n">
-        <v>5.29</v>
-      </c>
+        <v>3.15</v>
+      </c>
+      <c r="X9" s="10" t="n"/>
       <c r="Y9" s="10" t="n">
-        <v>23.67</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="10">
@@ -3242,306 +3278,383 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>4.06</v>
+        <v>4.63</v>
       </c>
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>6.38</v>
+        <v>7.91</v>
       </c>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>5.3</v>
+        <v>4.63</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>13.18</v>
+        <v>13.79</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>10.21</v>
+        <v>12.15</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>5.74</v>
+        <v>5.89</v>
       </c>
       <c r="N10" s="10" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.82</v>
+        <v>0.53</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q10" s="10" t="n">
-        <v>4.61</v>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="Q10" s="10" t="n"/>
       <c r="R10" s="10" t="n">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
       <c r="S10" s="10" t="n">
         <v>3.62</v>
       </c>
       <c r="T10" s="10" t="n">
-        <v>5.07</v>
+        <v>7.62</v>
       </c>
       <c r="U10" s="10" t="n"/>
       <c r="V10" s="10" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="W10" s="10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X10" s="10" t="n">
         <v>5.76</v>
       </c>
-      <c r="W10" s="10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X10" s="10" t="n">
-        <v>4.61</v>
-      </c>
       <c r="Y10" s="10" t="n">
-        <v>20.04</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte | medio-alto</t>
+          <t>null-Outros | medio-alto</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="D11" s="10" t="n"/>
+        <v>3.28</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.68</v>
+      </c>
       <c r="E11" s="10" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4.54</v>
+        <v>5.45</v>
       </c>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n">
-        <v>8.210000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>33.81</v>
+        <v>25.27</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>5.73</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>8.130000000000001</v>
+        <v>4.61</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>5.88</v>
+        <v>9.17</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Q11" s="10" t="n">
-        <v>7</v>
-      </c>
+        <v>0.64</v>
+      </c>
+      <c r="Q11" s="10" t="n"/>
       <c r="R11" s="10" t="n">
         <v>4.6</v>
       </c>
       <c r="S11" s="10" t="n">
-        <v>4.44</v>
+        <v>4.01</v>
       </c>
       <c r="T11" s="10" t="n">
-        <v>4.39</v>
+        <v>5.16</v>
       </c>
       <c r="U11" s="10" t="n"/>
       <c r="V11" s="10" t="n">
-        <v>3.45</v>
+        <v>4.92</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>5.77</v>
+        <v>4.13</v>
       </c>
       <c r="Y11" s="10" t="n">
-        <v>15.45</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros | alto</t>
+          <t>SC-Litoral-Norte | medio-alto</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="10" t="n"/>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="10" t="n"/>
-      <c r="S12" s="10" t="n"/>
-      <c r="T12" s="10" t="n"/>
-      <c r="U12" s="10" t="n"/>
-      <c r="V12" s="10" t="n"/>
-      <c r="W12" s="10" t="n"/>
-      <c r="X12" s="10" t="n"/>
-      <c r="Y12" s="10" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <v>18.79</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa | medio</t>
+          <t>SC-Outros | alto</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="10" t="n">
-        <v>5.14</v>
-      </c>
+      <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n">
-        <v>5.01</v>
-      </c>
+      <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>10.62</v>
-      </c>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n">
-        <v>1.22</v>
-      </c>
+      <c r="P13" s="10" t="n"/>
       <c r="Q13" s="10" t="n"/>
       <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>6.13</v>
-      </c>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
       <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="W13" s="10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="Y13" s="10" t="n">
-        <v>18.95</v>
-      </c>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SP-Capital | medio-alto</t>
+          <t>SC-Floripa | medio</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3.81</v>
+        <v>5.14</v>
       </c>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n">
-        <v>7.27</v>
+        <v>5.01</v>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n">
-        <v>9.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>7.22</v>
+        <v>4.25</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>10.8</v>
+        <v>10.62</v>
       </c>
       <c r="K14" s="10" t="n"/>
       <c r="L14" s="10" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>7.22</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>9.35</v>
+        <v>10.8</v>
       </c>
       <c r="O14" s="10" t="n"/>
       <c r="P14" s="10" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="Q14" s="10" t="n"/>
       <c r="R14" s="10" t="n"/>
       <c r="S14" s="10" t="n">
-        <v>4.11</v>
+        <v>3.3</v>
       </c>
       <c r="T14" s="10" t="n">
-        <v>4.88</v>
+        <v>6.13</v>
       </c>
       <c r="U14" s="10" t="n"/>
       <c r="V14" s="10" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="W14" s="10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <v>18.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SP-Capital | medio-alto</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="W14" s="10" t="n">
+      <c r="W15" s="10" t="n">
         <v>1.14</v>
       </c>
-      <c r="X14" s="10" t="n">
+      <c r="X15" s="10" t="n">
         <v>5.92</v>
       </c>
-      <c r="Y14" s="10" t="n">
+      <c r="Y15" s="10" t="n">
         <v>22.23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y14"/>
+  <autoFilter ref="A3:Y15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/analises-cross-projeto/benchmarks-estratificados/benchmarks-estratificados.xlsx
+++ b/analises-cross-projeto/benchmarks-estratificados/benchmarks-estratificados.xlsx
@@ -17,10 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'REGIAO'!$A$3:$J$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'REGIAO_PADRAO'!$A$3:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REGIAO_PADRAO_TIPOL'!$A$4:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'REGIAO_PADRAO'!$A$3:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REGIAO_PADRAO_TIPOL'!$A$4:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CLIENTE'!$A$3:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MATRIZ_MG'!$A$3:$Y$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MATRIZ_MG'!$A$3:$Y$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado 19/04/2026 09:15 . 131 projetos . 48 combinacoes</t>
+          <t>Gerado 19/04/2026 10:20 . 131 projetos . 45 combinacoes</t>
         </is>
       </c>
     </row>
@@ -706,16 +706,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1983.37</v>
+        <v>1519.6044</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>3100.1619</v>
+        <v>2758.48</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3462.55</v>
+        <v>3443.27</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>3799.28</v>
@@ -724,14 +724,14 @@
         <v>4888.48</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>7665.16</v>
+        <v>7957.795</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>25675656.81</v>
+        <v>25430694.8313</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>pass(5), mussi(4), amalfi(3)</t>
+          <t>pass(5), chiquetti(4), mussi(4)</t>
         </is>
       </c>
     </row>
@@ -742,16 +742,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2271.01</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2940.01</v>
+        <v>3217.76</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3755.78</v>
+        <v>3799.395</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>5246.69</v>
@@ -760,14 +760,14 @@
         <v>7668.2</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>9522.33</v>
+        <v>9133.245000000001</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>38409996.88</v>
+        <v>37718511.135</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>nova(4), blue(2), neuhaus(2)</t>
+          <t>nova(4), blue(2), chiquetti(2)</t>
         </is>
       </c>
     </row>
@@ -814,68 +814,68 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1917.5902</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2662.81</v>
+        <v>2781.34</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3401.76</v>
+        <v>3346.235</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4196.73</v>
+        <v>3784.64</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>7159.6961</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>6681.54</v>
+        <v>6868.635</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>23266450.125</v>
+        <v>25287249.72</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>grandezza(2), all(1), amalfi(1)</t>
+          <t>grandezza(2), paludo(2), all(1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>null-Outros</t>
+          <t>SP-Capital</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1519.6044</v>
+        <v>2974.22</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2781.34</v>
+        <v>2974.22</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2974.48</v>
+        <v>3028.41</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3515.51</v>
+        <v>3082.6</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>4346.61</v>
+        <v>3082.6</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>10609.48</v>
+        <v>6001.7</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>30584964.89</v>
+        <v>15642592.72</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>be(1), by(1), chiquetti(1)</t>
+          <t>indepy(2), macom(2), ajr(1)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>2624.8</v>
@@ -895,7 +895,7 @@
         <v>2624.8</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3650.32</v>
+        <v>3178.495</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>3732.19</v>
@@ -904,86 +904,86 @@
         <v>3732.19</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>7040.19</v>
+        <v>7946.51</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>18479084.15</v>
+        <v>25759756.415</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>mtf(2), paludo(2), chiquetti(1)</t>
+          <t>mtf(2), ck(1), paludo(1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SP-Capital</t>
+          <t>SC-Oeste</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2974.22</v>
+        <v>1604.0213</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2974.22</v>
+        <v>1604.0213</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3028.41</v>
+        <v>2529.9156</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3082.6</v>
+        <v>3455.81</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>3082.6</v>
+        <v>3455.81</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>6001.7</v>
+        <v>33399.665</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>15642592.72</v>
+        <v>56098317.04</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>indepy(2), macom(2), ajr(1)</t>
+          <t>santa(3), pavcor(1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SC-Oeste</t>
+          <t>RS-Serra</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>1604.0213</v>
+        <v>3134.37</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1604.0213</v>
+        <v>3134.37</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2529.9156</v>
+        <v>3650.32</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3455.81</v>
+        <v>5219.45</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3455.81</v>
+        <v>5219.45</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>33399.665</v>
+        <v>3972.3</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>56098317.04</v>
+        <v>12450664.73</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>santa(3), pavcor(1)</t>
+          <t>paludo(2), colline(1)</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>2455.59</v>
@@ -1111,14 +1111,14 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>ck(3), amalfi(2), chiquetti(2)</t>
+          <t>chiquetti(3), ck(3), amalfi(2)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1127,105 +1127,105 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3378.4464</v>
+        <v>2758.48</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3378.4464</v>
+        <v>3232.2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3628.6474</v>
+        <v>3462.55</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>4358.23</v>
+        <v>3722.92</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>4358.23</v>
+        <v>3799.28</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>9490.65</v>
+        <v>7193.62</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>ck(3), cn(2), adore(1)</t>
+          <t>pass(3), inbrasul(2), mussi(2)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2758.48</v>
+        <v>3217.76</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3232.2</v>
+        <v>3843.01</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3462.55</v>
+        <v>4642.46</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>3722.92</v>
+        <v>6091.07</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>3799.28</v>
+        <v>6123.12</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>7013.06</v>
+        <v>7964.39</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>pass(3), inbrasul(2), mussi(2)</t>
+          <t>nova(3), blue(2), chiquetti(2)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3217.76</v>
+        <v>3378.4464</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3843.01</v>
+        <v>3378.4464</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4642.46</v>
+        <v>3628.6474</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>6091.07</v>
+        <v>4358.23</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>6123.12</v>
+        <v>4358.23</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>7964.39</v>
+        <v>9490.65</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>nova(3), blue(2), chiquetti(1)</t>
+          <t>ck(3), cn(2), adore(1)</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>2549.1</v>
@@ -1250,16 +1250,16 @@
         <v>2940.01</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3390.04</v>
+        <v>3483.98</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>3755.78</v>
+        <v>4346.61</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>7668.2</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>13025.795</v>
+        <v>12828.33</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -1270,38 +1270,38 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Litoral-Norte</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>4864.6625</v>
+        <v>1917.5902</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>4864.6625</v>
+        <v>2662.81</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4864.6625</v>
+        <v>2877.91</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4864.6625</v>
+        <v>3515.51</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4864.6625</v>
+        <v>7159.6961</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>19500.94</v>
+        <v>6702.12</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>cambert(2), adore(1), beco(1)</t>
+          <t>paludo(2), all(1), amalfi(1)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>3290.71</v>
@@ -1335,7 +1335,7 @@
         <v>4196.73</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>6681.54</v>
+        <v>9780.735000000001</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1346,183 +1346,119 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>null-Outros</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2781.34</v>
+        <v>4864.6625</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2781.34</v>
+        <v>4864.6625</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3244.995</v>
+        <v>4864.6625</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4346.61</v>
+        <v>4864.6625</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4346.61</v>
+        <v>4864.6625</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>8609.299999999999</v>
+        <v>19500.94</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>be(1), by(1), gdi(1)</t>
+          <t>cambert(2), adore(1), beco(1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1917.5902</v>
+        <v>2271.01</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1917.5902</v>
+        <v>2271.01</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2662.81</v>
+        <v>2534.04</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>7159.6961</v>
+        <v>2797.07</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>7159.6961</v>
+        <v>2797.07</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>6140.53</v>
+        <v>12953.8</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>all(1), amalfi(1), grandezza(1)</t>
+          <t>fg(1), libra(1), neuhaus(1)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros</t>
+          <t>SP-Capital</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="8" t="n"/>
+      <c r="D13" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>3028.41</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>5179.985</v>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>chiquetti(1), ck(1), mtf(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SC-Floripa</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>2271.01</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>2271.01</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>2534.04</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>2797.07</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>2797.07</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>12953.8</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>fg(1), libra(1), neuhaus(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SP-Capital</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>2974.22</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>2974.22</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>3028.41</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>3082.6</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>3082.6</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>5179.985</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
           <t>macom(2), indepy(1)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J15"/>
+  <autoFilter ref="A3:J13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -1537,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1647,7 +1583,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2455.59</v>
@@ -1672,7 +1608,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ck(3), amalfi(2), chiquetti(2)</t>
+          <t>chiquetti(3), ck(3), amalfi(2)</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1629,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>3217.76</v>
@@ -1718,14 +1654,14 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>nova(3), blue(2), chiquetti(1)</t>
+          <t>nova(3), blue(2), chiquetti(2)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa</t>
+          <t>SC-Vale-Itajai</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1739,39 +1675,39 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2940.01</v>
+        <v>2758.48</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2940.01</v>
+        <v>3232.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3619.88</v>
+        <v>3595.675</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7668.2</v>
+        <v>3722.92</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>7668.2</v>
+        <v>3799.28</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>9116.129999999999</v>
+        <v>7010.46</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>viva4(2), all(1), arv(1)</t>
+          <t>inbrasul(2), pass(2), be(1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai</t>
+          <t>SC-Floripa</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1788,29 +1724,29 @@
         <v>10</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2758.48</v>
+        <v>2940.01</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3232.2</v>
+        <v>2940.01</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>3595.675</v>
+        <v>3619.88</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>3722.92</v>
+        <v>7668.2</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>3799.28</v>
+        <v>7668.2</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>7007.86</v>
+        <v>9116.129999999999</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>inbrasul(2), pass(2), brasin(1)</t>
+          <t>viva4(2), all(1), arv(1)</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1799,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Litoral-Norte</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1877,39 +1813,39 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4864.6625</v>
+        <v>3290.71</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>4864.6625</v>
+        <v>3290.71</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>4864.6625</v>
+        <v>3593.2</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>4864.6625</v>
+        <v>4196.73</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>4864.6625</v>
+        <v>4196.73</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>19500.94</v>
+        <v>9780.735000000001</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>cambert(2), adore(1), beco(1)</t>
+          <t>brasin(1), etr(1), eze(1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1926,36 +1862,36 @@
         <v>7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3290.71</v>
+        <v>4864.6625</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3290.71</v>
+        <v>4864.6625</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3593.2</v>
+        <v>4864.6625</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4196.73</v>
+        <v>4864.6625</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>4196.73</v>
+        <v>4864.6625</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>6681.54</v>
+        <v>19500.94</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>brasin(1), etr(1), eze(1)</t>
+          <t>cambert(2), adore(1), beco(1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>null-Outros</t>
+          <t>SC-Litoral-Norte</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1969,16 +1905,16 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="7" t="n">
+        <v>1917.5902</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>1917.5902</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>2781.34</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>2781.34</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>3148.425</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>3515.51</v>
@@ -1987,21 +1923,21 @@
         <v>3515.51</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>7524.255</v>
+        <v>6348.51</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>85.5</v>
+        <v>78.5</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>be(1), by(1), holze(1)</t>
+          <t>amalfi(1), by(1), grandezza(1)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-BC</t>
+          <t>SC-Litoral-Norte</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2011,43 +1947,43 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_medio_alto</t>
+          <t>residencial_vertical_alto</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3378.4464</v>
+        <v>2662.81</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>3378.4464</v>
+        <v>2662.81</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3378.4464</v>
+        <v>2974.48</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>3378.4464</v>
+        <v>7159.6961</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>3378.4464</v>
+        <v>7159.6961</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>12972.67</v>
+        <v>7055.73</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>cln(1), cn(1), fonseca(1)</t>
+          <t>all(1), mabrem(1), paludo(1)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte</t>
+          <t>SC-BC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2057,36 +1993,36 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_alto</t>
+          <t>residencial_vertical_medio_alto</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2662.81</v>
+        <v>3378.4464</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>2662.81</v>
+        <v>3378.4464</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>4911.253</v>
+        <v>3378.4464</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>7159.6961</v>
+        <v>3378.4464</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>7159.6961</v>
+        <v>3378.4464</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>4229.335</v>
+        <v>12972.67</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>all(1), paludo(1), thozen(1)</t>
+          <t>cln(1), cn(1), fonseca(1)</t>
         </is>
       </c>
     </row>
@@ -2139,81 +2075,49 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros</t>
+          <t>SP-Capital</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>residencial_vertical_alto</t>
+          <t>residencial_vertical_medio_alto</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="E16" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>2974.22</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>3028.41</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>3082.6</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>5179.985</v>
+      </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>chiquetti(1), ck(1), mtf(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SP-Capital</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>residencial_vertical_medio_alto</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>2974.22</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>2974.22</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>3028.41</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>3082.6</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>3082.6</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>5179.985</v>
-      </c>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
           <t>macom(2), indepy(1)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L17"/>
+  <autoFilter ref="A4:L16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -2655,7 +2559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2826,7 +2730,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>4</v>
@@ -2901,226 +2805,226 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SC-BC | medio-alto</t>
+          <t>SC-Vale-Itajai | medio-alto</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>3.06</v>
+        <v>1.32</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.48</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>7.13</v>
+        <v>7.57</v>
       </c>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n">
-        <v>9.119999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>4.67</v>
+        <v>3.54</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>12.59</v>
+        <v>13.06</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>11.88</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>5.18</v>
+        <v>5.36</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>7.19</v>
+        <v>10</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Q5" s="10" t="n"/>
+        <v>0.42</v>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <v>3.73</v>
+      </c>
       <c r="R5" s="10" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="S5" s="10" t="n">
-        <v>2.23</v>
+        <v>3.34</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>11.77</v>
+        <v>8.81</v>
       </c>
       <c r="U5" s="10" t="n"/>
       <c r="V5" s="10" t="n">
-        <v>1.66</v>
+        <v>4.51</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>5.29</v>
       </c>
       <c r="Y5" s="10" t="n">
-        <v>19.25</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SC-Vale-Itajai | medio-alto</t>
+          <t>SC-Floripa | alto</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1.32</v>
+        <v>0.7</v>
       </c>
       <c r="E6" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O6" s="10" t="n">
         <v>0.48</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>0.74</v>
-      </c>
       <c r="P6" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="Q6" s="10" t="n">
-        <v>3.73</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="Q6" s="10" t="n"/>
       <c r="R6" s="10" t="n">
-        <v>3.82</v>
+        <v>2.21</v>
       </c>
       <c r="S6" s="10" t="n">
-        <v>3.34</v>
+        <v>4.21</v>
       </c>
       <c r="T6" s="10" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="U6" s="10" t="n"/>
+        <v>4.07</v>
+      </c>
+      <c r="U6" s="10" t="n">
+        <v>0.23</v>
+      </c>
       <c r="V6" s="10" t="n">
-        <v>4.51</v>
+        <v>6.39</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>5.29</v>
+        <v>3.89</v>
       </c>
       <c r="Y6" s="10" t="n">
-        <v>20.08</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SC-Floripa | alto</t>
+          <t>SC-BC | medio-alto</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>3.66</v>
+        <v>4.67</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.7</v>
+        <v>3.06</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>3.83</v>
-      </c>
+        <v>7.13</v>
+      </c>
+      <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n">
-        <v>8.380000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>3.27</v>
+        <v>4.67</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>20.3</v>
+        <v>12.59</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>3.33</v>
+        <v>11.88</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>5.32</v>
+        <v>5.18</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>9.99</v>
+        <v>7.19</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.48</v>
+        <v>1.35</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>1.1</v>
+        <v>0.29</v>
       </c>
       <c r="Q7" s="10" t="n"/>
       <c r="R7" s="10" t="n">
-        <v>2.21</v>
+        <v>4.12</v>
       </c>
       <c r="S7" s="10" t="n">
-        <v>4.21</v>
+        <v>2.23</v>
       </c>
       <c r="T7" s="10" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="U7" s="10" t="n">
-        <v>0.23</v>
-      </c>
+        <v>11.77</v>
+      </c>
+      <c r="U7" s="10" t="n"/>
       <c r="V7" s="10" t="n">
-        <v>6.39</v>
+        <v>1.66</v>
       </c>
       <c r="W7" s="10" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>3.89</v>
+        <v>5.29</v>
       </c>
       <c r="Y7" s="10" t="n">
-        <v>17.48</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="8">
@@ -3130,10 +3034,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0.93</v>
@@ -3142,37 +3046,37 @@
         <v>0.59</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>4.29</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8.789999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>10.9</v>
+        <v>11.15</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>7.79</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>5.38</v>
+        <v>4.86</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>10.72</v>
+        <v>10.26</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Q8" s="10" t="n">
         <v>5.07</v>
@@ -3181,94 +3085,104 @@
         <v>4.68</v>
       </c>
       <c r="S8" s="10" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="T8" s="10" t="n">
-        <v>7.96</v>
+        <v>7.94</v>
       </c>
       <c r="U8" s="10" t="n">
         <v>0.88</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>5.76</v>
+        <v>6.02</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>19.42</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SC-BC | alto</t>
+          <t>SC-Litoral-Norte | medio-alto</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>3.77</v>
+        <v>2.2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E9" s="10" t="n"/>
+        <v>0.65</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.41</v>
+      </c>
       <c r="F9" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G9" s="10" t="n"/>
+        <v>4.77</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>2.27</v>
+      </c>
       <c r="H9" s="10" t="n">
-        <v>8.56</v>
+        <v>7.79</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>9.279999999999999</v>
+        <v>3.16</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>15.21</v>
+        <v>33.81</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>7.93</v>
+        <v>5.73</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>5.63</v>
+        <v>1.44</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>6.42</v>
+        <v>5.48</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>0.68</v>
+        <v>9.17</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>4.29</v>
+        <v>0.93</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="Q9" s="10" t="n"/>
+        <v>0.64</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>10.27</v>
+      </c>
       <c r="R9" s="10" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="S9" s="10" t="n">
-        <v>3.06</v>
+        <v>4.44</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>9.31</v>
-      </c>
-      <c r="U9" s="10" t="n"/>
+        <v>4.69</v>
+      </c>
+      <c r="U9" s="10" t="n">
+        <v>0.29</v>
+      </c>
       <c r="V9" s="10" t="n">
-        <v>3.84</v>
+        <v>3.45</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X9" s="10" t="n"/>
+        <v>1.75</v>
+      </c>
+      <c r="X9" s="10" t="n">
+        <v>5.2</v>
+      </c>
       <c r="Y9" s="10" t="n">
-        <v>11.86</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="10">
@@ -3278,7 +3192,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>4.63</v>
@@ -3345,316 +3259,200 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>null-Outros | medio-alto</t>
+          <t>SC-BC | alto</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.64</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n">
-        <v>5.45</v>
+        <v>3.1</v>
       </c>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n">
-        <v>7.98</v>
+        <v>8.56</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>3.48</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>25.27</v>
+        <v>15.21</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>5.73</v>
+        <v>7.93</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1.89</v>
+        <v>5.63</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>4.61</v>
+        <v>6.42</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>9.17</v>
+        <v>0.68</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.88</v>
+        <v>4.29</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="Q11" s="10" t="n"/>
       <c r="R11" s="10" t="n">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="S11" s="10" t="n">
-        <v>4.01</v>
+        <v>3.06</v>
       </c>
       <c r="T11" s="10" t="n">
-        <v>5.16</v>
+        <v>9.31</v>
       </c>
       <c r="U11" s="10" t="n"/>
       <c r="V11" s="10" t="n">
-        <v>4.92</v>
+        <v>3.84</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X11" s="10" t="n">
-        <v>4.13</v>
-      </c>
+        <v>3.15</v>
+      </c>
+      <c r="X11" s="10" t="n"/>
       <c r="Y11" s="10" t="n">
-        <v>19.07</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SC-Litoral-Norte | medio-alto</t>
+          <t>SC-Floripa | medio</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.3</v>
-      </c>
+        <v>5.14</v>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>2.27</v>
-      </c>
+        <v>5.01</v>
+      </c>
+      <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n">
-        <v>6.33</v>
+        <v>8.84</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3.16</v>
+        <v>4.25</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>4.94</v>
-      </c>
+        <v>10.62</v>
+      </c>
+      <c r="K12" s="10" t="n"/>
       <c r="L12" s="10" t="n">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>5.75</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>0.73</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="O12" s="10" t="n"/>
       <c r="P12" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>3.77</v>
-      </c>
+        <v>1.22</v>
+      </c>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
       <c r="S12" s="10" t="n">
-        <v>4.44</v>
+        <v>3.3</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" s="10" t="n">
-        <v>0.29</v>
-      </c>
+        <v>6.13</v>
+      </c>
+      <c r="U12" s="10" t="n"/>
       <c r="V12" s="10" t="n">
-        <v>2.06</v>
+        <v>5.61</v>
       </c>
       <c r="W12" s="10" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>5.93</v>
+        <v>7.13</v>
       </c>
       <c r="Y12" s="10" t="n">
-        <v>18.79</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SC-Outros | alto</t>
+          <t>SP-Capital | medio-alto</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="10" t="n"/>
+      <c r="C13" s="10" t="n">
+        <v>3.81</v>
+      </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
+      <c r="F13" s="10" t="n">
+        <v>7.27</v>
+      </c>
       <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>10.8</v>
+      </c>
       <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="10" t="n"/>
+      <c r="L13" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>9.35</v>
+      </c>
       <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
+      <c r="P13" s="10" t="n">
+        <v>0.49</v>
+      </c>
       <c r="Q13" s="10" t="n"/>
       <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
-      <c r="T13" s="10" t="n"/>
+      <c r="S13" s="10" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>4.88</v>
+      </c>
       <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n"/>
-      <c r="X13" s="10" t="n"/>
-      <c r="Y13" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SC-Floripa | medio</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M14" s="10" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="N14" s="10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Q14" s="10" t="n"/>
-      <c r="R14" s="10" t="n"/>
-      <c r="S14" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T14" s="10" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="U14" s="10" t="n"/>
-      <c r="V14" s="10" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="W14" s="10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X14" s="10" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="Y14" s="10" t="n">
-        <v>18.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SP-Capital | medio-alto</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M15" s="10" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="O15" s="10" t="n"/>
-      <c r="P15" s="10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="10" t="n"/>
-      <c r="S15" s="10" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="T15" s="10" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="U15" s="10" t="n"/>
-      <c r="V15" s="10" t="n">
+      <c r="V13" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W13" s="10" t="n">
         <v>1.14</v>
       </c>
-      <c r="X15" s="10" t="n">
+      <c r="X13" s="10" t="n">
         <v>5.92</v>
       </c>
-      <c r="Y15" s="10" t="n">
+      <c r="Y13" s="10" t="n">
         <v>22.23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y15"/>
+  <autoFilter ref="A3:Y13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
